--- a/output/pdf_financials_xlsx/PRV.UN.xlsx
+++ b/output/pdf_financials_xlsx/PRV.UN.xlsx
@@ -2366,43 +2366,43 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.000508</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000896</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000588</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.000777</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.002056</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.003744</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.004116</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.005302</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.005944</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.007531</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.013256</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.009069000000000001</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.013672</v>
       </c>
     </row>
     <row r="35">
@@ -2458,43 +2458,43 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.000508</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.000896</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000588</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.000777</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.002056</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.003744</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.004116</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.005302</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.005944</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.007531</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.013256</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.009069000000000001</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.013672</v>
       </c>
     </row>
     <row r="37">
@@ -3010,43 +3010,43 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.000508</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.00148</v>
+        <v>0.000584</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.002198</v>
+        <v>0.00161</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.003883</v>
+        <v>0.003106</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.006352</v>
+        <v>0.004296</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.009693999999999999</v>
+        <v>0.00595</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.009761000000000001</v>
+        <v>0.005645</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.011696</v>
+        <v>0.006394</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.010184</v>
+        <v>0.00424</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.013233</v>
+        <v>0.005702</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.019373</v>
+        <v>0.006117</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.017245</v>
+        <v>0.008175999999999999</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.020499</v>
+        <v>0.006827</v>
       </c>
     </row>
     <row r="49">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">

--- a/output/pdf_financials_xlsx/PRV.UN.xlsx
+++ b/output/pdf_financials_xlsx/PRV.UN.xlsx
@@ -2034,25 +2034,25 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>1.8e-05</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>2.4e-05</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>2.6e-05</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>4e-05</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>4.5e-05</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.000185</v>
+        <v>0.000237</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.000372</v>
+        <v>0.000569</v>
       </c>
       <c r="J28" s="1" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>-0.000134</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.004547</v>
+        <v>0.004565</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.018955</v>
+        <v>0.019007</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.015347</v>
+        <v>0.015544</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -5444,40 +5444,40 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>1.8e-05</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>2.4e-05</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>2.6e-05</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>4e-05</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>4.5e-05</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.000237</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.000569</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.000729</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.000789</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.000786</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.000835</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.000838</v>
       </c>
     </row>
     <row r="101">
@@ -17936,7 +17936,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -18090,7 +18094,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -20191,7 +20195,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -21245,7 +21249,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -22947,7 +22951,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -23028,7 +23036,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -24294,7 +24302,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -25493,7 +25505,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -28752,7 +28768,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -28833,7 +28853,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -31245,7 +31265,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -31326,7 +31350,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -33718,7 +33742,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -38014,7 +38042,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
           <t>-</t>
@@ -40240,7 +40272,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E425" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PRV.UN.xlsx
+++ b/output/pdf_financials_xlsx/PRV.UN.xlsx
@@ -2651,34 +2651,34 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.000474</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.000475</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.001895</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.001668</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.001635</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>1.1e-05</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.0005820000000000001</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.000139</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.000268</v>
       </c>
     </row>
     <row r="41">
@@ -2697,34 +2697,34 @@
         <v>0</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0</v>
+        <v>0.000474</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>0.000475</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>0.001895</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>0.001668</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0</v>
+        <v>0.001635</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0</v>
+        <v>1.1e-05</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>0.0005820000000000001</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0</v>
+        <v>0.000139</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>0</v>
+        <v>0.000268</v>
       </c>
     </row>
     <row r="42">
@@ -3019,34 +3019,34 @@
         <v>0.00161</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.003106</v>
+        <v>0.002632</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.004296</v>
+        <v>0.003821</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.00595</v>
+        <v>0.004055</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.005645</v>
+        <v>0.003977</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.006394</v>
+        <v>0.004759</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.00424</v>
+        <v>0.004229</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.005702</v>
+        <v>0.00512</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.006117</v>
+        <v>0.005978</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.008175999999999999</v>
+        <v>0.007976</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.006827</v>
+        <v>0.006559</v>
       </c>
     </row>
     <row r="49">
@@ -3606,22 +3606,22 @@
         <v>0</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0</v>
+        <v>0.002356</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0</v>
+        <v>0.002356</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0</v>
+        <v>0.002356</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>0</v>
+        <v>0.002356</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0</v>
+        <v>0.002356</v>
       </c>
       <c r="M60" s="3" t="n">
-        <v>0</v>
+        <v>0.002356</v>
       </c>
       <c r="N60" s="3" t="n">
         <v>0</v>
@@ -3652,22 +3652,22 @@
         <v>0.356055</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.4945</v>
+        <v>0.492144</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.617166</v>
+        <v>0.61481</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.973971</v>
+        <v>0.971615</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>1.017176</v>
+        <v>1.01482</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>1.009628</v>
+        <v>1.007272</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>0.974484</v>
+        <v>0.972128</v>
       </c>
       <c r="N61" s="3" t="n">
         <v>1.050822</v>
@@ -3910,43 +3910,43 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>2.5e-05</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0006489999999999999</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.000901</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.001991</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.001824</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.002404</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.003605</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.004099</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.004837</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.004614</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.004638</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.007385</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.006395</v>
       </c>
     </row>
     <row r="68">
@@ -3956,43 +3956,43 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0</v>
+        <v>2.5e-05</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0</v>
+        <v>0.0006489999999999999</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0</v>
+        <v>0.000901</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>0.001991</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>0.001824</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>0.002404</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>0.003605</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>0.004099</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>0.004837</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>0.004614</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0</v>
+        <v>0.004638</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0</v>
+        <v>0.007385</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0</v>
+        <v>0.006395</v>
       </c>
     </row>
     <row r="69">
@@ -4278,43 +4278,43 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>2.5e-05</v>
+        <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.003667</v>
+        <v>0.003018</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.004281</v>
+        <v>0.00338</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.009719</v>
+        <v>0.007728</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.009679</v>
+        <v>0.007854999999999999</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.02989</v>
+        <v>0.027486</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.03695</v>
+        <v>0.033345</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.020826</v>
+        <v>0.016727</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.039088</v>
+        <v>0.034251</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.08157</v>
+        <v>0.076956</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.120734</v>
+        <v>0.116096</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.163594</v>
+        <v>0.156209</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.26156</v>
+        <v>0.255165</v>
       </c>
     </row>
     <row r="76">
